--- a/USA Government Contract Opportunities.xlsx
+++ b/USA Government Contract Opportunities.xlsx
@@ -11,16 +11,24 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Federal Opportunities" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subcontracting" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K-12 IT Hardware" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All 50 State Portals" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bidder Roadmap" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Education Projects" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closed Awarded" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upcoming Forecasts" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Winning Contractors" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All 50 State Portals" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bidder Roadmap" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage Notes" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Federal Opportunities'!$A$4:$N$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Federal Opportunities'!$A$4:$N$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Subcontracting'!$A$4:$L$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'K-12 IT Hardware'!$A$4:$I$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'All 50 State Portals'!$A$4:$F$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Bidder Roadmap'!$A$4:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'State Education Projects'!$A$4:$G$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Closed Awarded'!$A$4:$J$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Upcoming Forecasts'!$A$4:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Winning Contractors'!$A$4:$H$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'All 50 State Portals'!$A$4:$F$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Bidder Roadmap'!$A$4:$G$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,10 +37,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="mmm d, yyyy"/>
+    <numFmt numFmtId="164" formatCode="mmm d, yyyy"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00;[Red]($#,##0.00);-"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -145,6 +153,11 @@
       <color rgb="0017202A"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="00B54708"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -214,7 +227,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -237,12 +250,26 @@
         <color rgb="00D8DEE8"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D8DEE8"/>
+      </top>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D8DEE8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -284,7 +311,7 @@
     <xf numFmtId="49" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -296,10 +323,16 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -338,6 +371,29 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,8 +496,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FederalOpportunities" displayName="FederalOpportunities" ref="A4:N17" headerRowCount="1">
-  <autoFilter ref="A4:N17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FederalOpportunities" displayName="FederalOpportunities" ref="A4:N19" headerRowCount="1">
+  <autoFilter ref="A4:N19"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Category"/>
     <tableColumn id="2" name="Title"/>
@@ -502,7 +558,61 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="StatePortals" displayName="StatePortals" ref="A4:F54" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RecentAwards" displayName="RecentAwards" ref="A4:J44" headerRowCount="1">
+  <autoFilter ref="A4:J44"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Category"/>
+    <tableColumn id="2" name="Award / Contract ID"/>
+    <tableColumn id="3" name="Description"/>
+    <tableColumn id="4" name="Agency"/>
+    <tableColumn id="5" name="Recipient"/>
+    <tableColumn id="6" name="NAICS Query Code"/>
+    <tableColumn id="7" name="Reported Start Date"/>
+    <tableColumn id="8" name="Amount (USD)"/>
+    <tableColumn id="9" name="Verified On"/>
+    <tableColumn id="10" name="USAspending Record"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="UpcomingForecasts" displayName="UpcomingForecasts" ref="A4:I16" headerRowCount="1">
+  <autoFilter ref="A4:I16"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Category"/>
+    <tableColumn id="2" name="Forecast ID"/>
+    <tableColumn id="3" name="Program / Requirement"/>
+    <tableColumn id="4" name="Agency"/>
+    <tableColumn id="5" name="NAICS"/>
+    <tableColumn id="6" name="Estimated Solicitation / Award Timing"/>
+    <tableColumn id="7" name="Status"/>
+    <tableColumn id="8" name="Verified On"/>
+    <tableColumn id="9" name="Official Forecast"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="WinningContractors" displayName="WinningContractors" ref="A4:H38" headerRowCount="1">
+  <autoFilter ref="A4:H38"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Contractor"/>
+    <tableColumn id="2" name="Awards in This Dataset"/>
+    <tableColumn id="3" name="Total Value in Dataset (USD)"/>
+    <tableColumn id="4" name="Awarding Agencies"/>
+    <tableColumn id="5" name="Categories"/>
+    <tableColumn id="6" name="Contract / Award IDs"/>
+    <tableColumn id="7" name="Source Scope"/>
+    <tableColumn id="8" name="Example Record"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="StatePortals" displayName="StatePortals" ref="A4:F54" headerRowCount="1">
   <autoFilter ref="A4:F54"/>
   <tableColumns count="6">
     <tableColumn id="1" name="State"/>
@@ -516,8 +626,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="BidderRoadmap" displayName="BidderRoadmap" ref="A4:G13" headerRowCount="1">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="BidderRoadmap" displayName="BidderRoadmap" ref="A4:G13" headerRowCount="1">
   <autoFilter ref="A4:G13"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Step"/>
@@ -839,67 +949,45 @@
     <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>USA Government Contract Opportunities</t>
+          <t>TenderTrack USA Opportunities</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Verified snapshot • researched September 18, 2026 • federal prime notices, subcontracting leads, K-12 school IT bids, and all 50 state portals</t>
+          <t>Verified September 18, 2026 • federal bids, subcontracts, K-12 technology, recent awards, upcoming forecasts, contractors, and all 50 state procurement routes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>13
+          <t>15
 Verified open federal notices</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>10
 Open SBA SubNet notices</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>2
-Open K-12 school IT bids</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="n"/>
+          <t>40
+Recent federal awards</t>
+        </is>
+      </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>50
-Official state portals mapped</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-    </row>
+          <t>12
+Upcoming DHS forecasts</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="8">
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -982,7 +1070,7 @@
     <row r="16">
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>This is a verified research snapshot, not a complete or live feed of every U.S. opportunity. The federal sweep was interrupted by a fetch-service failure, so only notices individually verified as open are listed. Facilities, medical supplies, and general supplies had no verified rows in this pass. State and local governments publish through separate portals. The K-12 IT-hardware sweep found only 2 verifiable open bids on the research date; most school device buying runs through state contracts and purchasing cooperatives, and the next refresh cycle is expected January to April 2027. Always confirm status, amendments, and deadline on the official source before acting.</t>
+          <t>This is a verified research snapshot, not a complete or live feed of every U.S. opportunity. Only notices individually verified as open are listed. Warehousing, furniture, furnishings/textiles, security, medical supplies, and office supplies had no verified federal rows in this pass. The 50-state sheet is a portal directory, not a live state-bid inventory. State, county, city, school, and university buyers publish through separate systems. The K-12 sweep found 2 open school technology bids, but neither is a confirmed laptop, desktop, printer, or copier purchase. No qualifying open college or university end-user device bid was verified. Most device buying runs through state contracts and cooperatives. Always confirm status, amendments, and deadline on the official source before acting.</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1097,610 @@
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;8 USA Government Contract Opportunities • snapshot 2026-09-18</oddFooter>
+    <oddFooter>&amp;C&amp;8 TenderTrack USA Opportunities • verified 2026-09-18</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Zero-to-Bid Roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Practical orientation for a person, LLC, company, or SMB. Requirements vary by buyer and solicitation; official notice terms control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Who Needs It</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>What to Prepare</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Typical Timing / Rule</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Do Not Miss</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Official Route</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="72" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Choose a business structure</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Any seller</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Ownership, state, registered agent, tax and liability plan</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>State-specific</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>An individual may sell in some settings, but entity and insurance requirements vary.</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Use your state's official business filing office.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Get EIN and business banking</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>Most businesses</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Entity records, responsible-party information, bank account</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>Keep legal name and address consistent across records.</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>Use official IRS and bank channels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Register the entity in SAM.gov</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Federal prime bidders</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Legal business name, TIN, physical address, banking, NAICS, ownership, CAGE validation</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Free; research found up to 10 to 12 business days; renew every 365 days</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>SAM registration is free. Do not share login credentials with a third party.</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>Open SAM.gov</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="72" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Receive a UEI</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Federal prime bidders</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Issued through SAM registration</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Often immediate if validation passes; manual review may take longer</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>A UEI-only record does not equal full registration for prime bidding.</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>Open SAM.gov</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="72" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Select NAICS and check size</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Federal and many state bidders</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Capabilities, revenue/employee size, relevant codes</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Before bidding</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>A company can be small under one NAICS and not another.</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>Use SBA's official size standards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="72" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Assess certifications</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>Eligible small businesses</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Ownership/control evidence, location, veteran or women-owned eligibility where applicable</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>Can take weeks or months</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>Never claim a certification or set-aside status you do not hold.</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>Use SBA certification channels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="72" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Register on buyer portals</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>State/local and some prime subcontractors</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Vendor profile, W-9, commodity codes, insurance, licenses</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Portal-specific</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Each state, county, city, authority, and prime may use a separate system.</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>Use the All 50 State Portals tab and official buyer links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="72" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Build a bid/no-bid checklist</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Everyone</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Capability match, past performance, staffing, pricing, schedule, bond/insurance capacity</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Before every pursuit</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>Check notice type. Sources Sought and RFIs usually are not priced bid invitations.</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>Read the complete official notice and every amendment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="72" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Submit and retain proof</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Qualified bidders</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Signed forms, pricing, technical response, reps/certs, attachments</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Before exact deadline/time zone</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Late submissions are commonly rejected. Follow the required channel exactly.</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>Use only the submission method named in the notice.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G13"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 TenderTrack USA Opportunities • verified 2026-09-18</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coverage, Definitions &amp; Caveats</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Read this sheet before treating the workbook as a complete market inventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>WHAT IS INCLUDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>15 federal notices individually confirmed open after September 18, 2026; 10 SBA SubNet notices; 2 K-12 school technology bids; 40 recent federal awards; 12 DHS acquisition forecasts; a contractor directory derived from those awards; and all 50 state procurement systems mapped with access status. This is a dated snapshot, not a complete live feed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1"/>
+    <row r="7" ht="34" customHeight="1"/>
+    <row r="9" ht="28" customHeight="1">
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>WHAT IS NOT INCLUDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>This is not every active SAM.gov notice, every city or county portal, every prime-contractor supplier portal, or every live state solicitation. Warehousing, furniture, furnishings/textiles, security services, medical supplies, and office supplies contain zero verified federal rows rather than guessed or stale listings. The school section has no verified open laptop, desktop, printer, or copier purchase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1"/>
+    <row r="12" ht="34" customHeight="1"/>
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>NOTICE TYPES</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>Solicitation / Combined Synopsis-Solicitation: generally actionable competition; read the full package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>Sources Sought / RFI: market research and capability discovery; usually not a priced bid invitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>Commercial Solutions Opening: may stay open for an extended period and accept solutions under special procedures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>STATE DIRECTORY STATUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>Public search verified: opportunity browsing was confirmed without login.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>Login required: official guidance routes users through authentication before search or response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>Partial: some information is public, but documents or response steps may require registration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>Not fully verified: portal or no-login behavior could not be confirmed; blank URLs were intentionally not guessed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>ACTION RULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="B26" s="29" t="inlineStr">
+        <is>
+          <t>Before bidding, open the official source and confirm that the notice remains active, review all amendments and attachments, verify eligibility and set-aside status, note the exact submission deadline and time zone, and use the buyer's required submission channel. A listed opportunity is not a promise of eligibility or award.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1"/>
+    <row r="28" ht="34" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B10:E12"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B26:E28"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B5:E7"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B14:E14"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 TenderTrack USA Opportunities • verified 2026-09-18</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1024,7 +1715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1046,14 +1737,14 @@
     <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Federal Opportunities</t>
+          <t>Open Federal Bids</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>13 notices individually verified open on September 18, 2026. Use the official notice to confirm amendments, attachments, and current status.</t>
+          <t>15 notices individually verified open on September 18, 2026. Use the official source to confirm amendments, attachments, restrictions, and current status.</t>
         </is>
       </c>
     </row>
@@ -1139,57 +1830,55 @@
     <row r="5" ht="72" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>IT services</t>
+          <t>Building Construction</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>DA01-Compensation &amp; Pension (C&amp;P) Product Line Help Desk Tier 2 and Deployment Support Services 2.0</t>
+          <t>Table Mountain T1 and B9 Renovation</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>36C10B26Q0725</t>
+          <t>1331L526TBRENOVAT</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Veterans Affairs, Department of</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>Technology Acquisition Center NJ (36C10B)</t>
-        </is>
-      </c>
+          <t>Department of Commerce</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr"/>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Sources Sought</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="G5" s="16" t="inlineStr">
         <is>
-          <t>541512</t>
+          <t>236220</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I5" s="17" t="n">
-        <v>46282</v>
-      </c>
-      <c r="J5" s="17" t="n">
-        <v>46296</v>
+          <t>Total Small Business</t>
+        </is>
+      </c>
+      <c r="I5" s="37" t="inlineStr"/>
+      <c r="J5" s="37" t="n">
+        <v>46286</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="L5" s="15" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>Longmont, CO 80503</t>
+        </is>
+      </c>
       <c r="M5" s="15" t="inlineStr">
         <is>
-          <t>RFI for Tier 2 help desk and deployment support services for the VA Compensation and Pension product line (draft PWS attached).</t>
+          <t>No additional caveat recorded; official notice controls.</t>
         </is>
       </c>
       <c r="N5" s="18" t="inlineStr">
@@ -1201,57 +1890,55 @@
     <row r="6" ht="72" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>IT services</t>
+          <t>Building Construction</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>CFBLNET</t>
+          <t>Replace Window B4311</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>HC104709250103</t>
+          <t>FA466126R0011</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>Dept of Defense</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>Defense Information Systems Agency</t>
-        </is>
-      </c>
+          <t>Department of Defense, Department of the Air Force</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr"/>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>Sources Sought</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
-          <t>541512</t>
+          <t>236220</t>
         </is>
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I6" s="21" t="n">
-        <v>46282</v>
-      </c>
-      <c r="J6" s="21" t="n">
-        <v>46295</v>
+          <t>Total Small Business</t>
+        </is>
+      </c>
+      <c r="I6" s="38" t="inlineStr"/>
+      <c r="J6" s="38" t="n">
+        <v>46287</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="L6" s="19" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L6" s="19" t="inlineStr">
+        <is>
+          <t>Dyess AFB, TX 79607</t>
+        </is>
+      </c>
       <c r="M6" s="19" t="inlineStr">
         <is>
-          <t>Full range of CFBLNet Design Transition and Operation (DTO) capabilities supporting mission partner network interoperability.</t>
+          <t>No additional caveat recorded; official notice controls.</t>
         </is>
       </c>
       <c r="N6" s="22" t="inlineStr">
@@ -1263,57 +1950,55 @@
     <row r="7" ht="72" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>IT services</t>
+          <t>Building Construction</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>DCSA Innovation Gateway</t>
+          <t>Patten Hall Renovations - United States Merchant Marine Academy (USMMA)</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>HS0021-26-CSO-DCSA</t>
+          <t>6923G226Q000034</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Dept of Defense</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>Defense CI and Security Agency</t>
-        </is>
-      </c>
+          <t>Department of Transportation, Maritime Administration</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr"/>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>Solicitation</t>
+          <t>Combined Synopsis/Solicitation</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
-          <t>541512</t>
+          <t>236220</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>Full and open</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="n">
-        <v>46275</v>
-      </c>
-      <c r="J7" s="17" t="n">
-        <v>48021</v>
+          <t>Total Small Business</t>
+        </is>
+      </c>
+      <c r="I7" s="37" t="inlineStr"/>
+      <c r="J7" s="37" t="n">
+        <v>46287</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>1738</v>
-      </c>
-      <c r="L7" s="15" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <t>Kings Point, NY 11024</t>
+        </is>
+      </c>
       <c r="M7" s="15" t="inlineStr">
         <is>
-          <t>Competitive commercial solutions opening for prototype projects under Other Transaction Agreements in digital transformation data integration and cyber.</t>
+          <t>No additional caveat recorded; official notice controls.</t>
         </is>
       </c>
       <c r="N7" s="18" t="inlineStr">
@@ -1325,57 +2010,55 @@
     <row r="8" ht="72" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>IT services</t>
+          <t>Building Construction</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Wideband Remote Monitoring Sensor (WRMS) Enhancement and Sustainment (E&amp;S)</t>
+          <t>FEMA Region 6 Regional Watch Center Renovations</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>832675541</t>
+          <t>70FBR626R00000012</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>Dept of Defense</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>IT Contracting Division - PL83</t>
-        </is>
-      </c>
+          <t>Department of Homeland Security, Federal Emergency Management Agency Region 6</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr"/>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>Sources Sought</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>541512</t>
+          <t>236220</t>
         </is>
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I8" s="21" t="n">
-        <v>46274</v>
-      </c>
-      <c r="J8" s="21" t="n">
+          <t>SBA-certified Women-Owned Small Business (WOSB)</t>
+        </is>
+      </c>
+      <c r="I8" s="38" t="inlineStr"/>
+      <c r="J8" s="38" t="n">
         <v>46288</v>
       </c>
       <c r="K8" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="L8" s="19" t="inlineStr"/>
+      <c r="L8" s="19" t="inlineStr">
+        <is>
+          <t>Denton, TX 76209</t>
+        </is>
+      </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
-          <t>Sustainment and enhancement of the fielded WRMS v3.x satellite network spectrum monitoring software (draft PWS attached).</t>
+          <t>No additional caveat recorded; official notice controls.</t>
         </is>
       </c>
       <c r="N8" s="22" t="inlineStr">
@@ -1387,12 +2070,12 @@
     <row r="9" ht="72" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>IT services</t>
+          <t>IT Services &amp; Equipment</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Think Trends Software as an Agentic AI and Document Intelligence Solution</t>
+          <t>AEMS Think Trends Licenses (Brand Name)</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -1402,14 +2085,10 @@
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Health and Human Services, Department of</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>FDA Office of Acquisition and Grant Services</t>
-        </is>
-      </c>
+          <t>Food and Drug Administration, Office of Acquisition and Grant Services</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr"/>
       <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Combined Synopsis/Solicitation</t>
@@ -1420,28 +2099,18 @@
           <t>541519</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>Full and open</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>46282</v>
-      </c>
-      <c r="J9" s="17" t="n">
+      <c r="H9" s="15" t="inlineStr"/>
+      <c r="I9" s="37" t="inlineStr"/>
+      <c r="J9" s="37" t="n">
         <v>46289</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="L9" s="15" t="inlineStr">
-        <is>
-          <t>Silver Spring, MD</t>
-        </is>
-      </c>
+      <c r="L9" s="15" t="inlineStr"/>
       <c r="M9" s="15" t="inlineStr">
         <is>
-          <t>Agentic AI document intelligence for adverse event processing with OCR extraction and FOIA redaction capabilities.</t>
+          <t>Agentic AI and document intelligence (Think Trends) for FDA adverse-event processing across CDER/CBER/CDRH/CTP/CVM/HFP. Verified via fresh search hits crawled ~2 hours ago: posted ~Sep 17, 2026, deadline in 6 days. Direct SAM.gov workspace URL not recoverable this turn; url points to the notice detail mirror.</t>
         </is>
       </c>
       <c r="N9" s="18" t="inlineStr">
@@ -1453,57 +2122,55 @@
     <row r="10" ht="72" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>Professional services</t>
+          <t>Building Construction</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Communications Uses Market Rent Study</t>
+          <t>Repair Water Tanks Deficiencies</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>12318726Q0077</t>
+          <t>36C24826R0133</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>Agriculture, Department of</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>USDA Forest Service</t>
-        </is>
-      </c>
+          <t>Department of Veterans Affairs, Network Contracting Office 8</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr"/>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>Combined Synopsis/Solicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
-          <t>541611</t>
+          <t>236220</t>
         </is>
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>Full and open</t>
-        </is>
-      </c>
-      <c r="I10" s="21" t="n">
-        <v>46282</v>
-      </c>
-      <c r="J10" s="21" t="n">
-        <v>46290</v>
+          <t>Service-Disabled Veteran-Owned Small Business (SDVOSB)</t>
+        </is>
+      </c>
+      <c r="I10" s="38" t="inlineStr"/>
+      <c r="J10" s="38" t="n">
+        <v>46289</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="L10" s="19" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="L10" s="19" t="inlineStr">
+        <is>
+          <t>San Juan, PR 00921</t>
+        </is>
+      </c>
       <c r="M10" s="19" t="inlineStr">
         <is>
-          <t>Market rent survey for wireless communications use authorizations across Forest Service communications sites.</t>
+          <t>No additional caveat recorded; official notice controls.</t>
         </is>
       </c>
       <c r="N10" s="22" t="inlineStr">
@@ -1515,29 +2182,25 @@
     <row r="11" ht="72" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Table Mountain T1 and B9 Renovation</t>
+          <t>Communications Uses Market Rent Study</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>1331L526TBRENOVAT</t>
+          <t>12318726Q0077</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>COMMERCE, DEPARTMENT OF</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>DEPT OF COMMERCE SSPO</t>
-        </is>
-      </c>
+          <t>USDA Forest Service</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr"/>
       <c r="F11" s="15" t="inlineStr">
         <is>
           <t>Solicitation</t>
@@ -1545,31 +2208,21 @@
       </c>
       <c r="G11" s="16" t="inlineStr">
         <is>
-          <t>236220</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>Total Small Business Set-Aside (FAR 19.5)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>46275</v>
-      </c>
-      <c r="J11" s="17" t="n">
-        <v>46286</v>
+          <t>541611</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr"/>
+      <c r="I11" s="37" t="inlineStr"/>
+      <c r="J11" s="37" t="n">
+        <v>46290</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" s="15" t="inlineStr">
-        <is>
-          <t>Longmont, CO 80503</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="L11" s="15" t="inlineStr"/>
       <c r="M11" s="15" t="inlineStr">
         <is>
-          <t>Renovate two buildings (T1 and B9) at Table Mountain, Longmont CO; 100% small business set-aside solicitation.</t>
+          <t>Firm-fixed-price contract for a Communications Uses Market Rent Study ensuring annual land-use rental fees for ~3,900 wireless communications authorizations across 1,400 sites reflect market economics (per Section 504(g) of FLEMA). Proposals due September 25, 2026, 2:00 PM ET, emailed to cassandra.carey@usda.gov; best-value award; pre-bid meeting held Sep 15, 2026. Verified via fresh search hits including the SAM.gov solicitation PDF mirror; url is the verbatim mirror link to the SAM.gov solicitation PDF.</t>
         </is>
       </c>
       <c r="N11" s="18" t="inlineStr">
@@ -1581,29 +2234,25 @@
     <row r="12" ht="72" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>Building Construction</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>iHouse Apartment Construction</t>
+          <t>REPAIR LIVE FIRE TRAINING FACILITY AIRCRAFT MOCK-UP</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>75H70126R00026</t>
+          <t>FA665626R0006</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>HEALTH AND HUMAN SERVICES, DEPARTMENT OF</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>Indian Health Service, Division of Engineering Services - Seattle</t>
-        </is>
-      </c>
+          <t>Department of Defense, Department of the Air Force, Air Force Reserve Command</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr"/>
       <c r="F12" s="19" t="inlineStr">
         <is>
           <t>Solicitation</t>
@@ -1616,26 +2265,24 @@
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>Indian Small Business Economic Enterprise (ISBEE) Set-Aside</t>
-        </is>
-      </c>
-      <c r="I12" s="21" t="n">
-        <v>46218</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>46303</v>
+          <t>SBA-certified Women-Owned Small Business (WOSB)</t>
+        </is>
+      </c>
+      <c r="I12" s="38" t="inlineStr"/>
+      <c r="J12" s="38" t="n">
+        <v>46290</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="L12" s="19" t="inlineStr">
         <is>
-          <t>Tonalea, AZ 86044</t>
+          <t>Youngstown Air Reserve Station, Vienna, OH 44473</t>
         </is>
       </c>
       <c r="M12" s="19" t="inlineStr">
         <is>
-          <t>Adapt and construct a 19-unit apartment building at Indian Rte 6290, Tonalea AZ; magnitude $5M-$10M; 365 calendar days; firm fixed price.</t>
+          <t>No additional caveat recorded; official notice controls.</t>
         </is>
       </c>
       <c r="N12" s="22" t="inlineStr">
@@ -1647,61 +2294,55 @@
     <row r="13" ht="72" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>Laboratories</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>FEMA Region 6 Regional Watch Center Renovations</t>
+          <t>Sample Testing Blanket Purchase Agreement</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>70FBR626R00000012</t>
+          <t>W9127N26QA092</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>HOMELAND SECURITY, DEPARTMENT OF</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>FEDERAL EMERGENCY MANAGEMENT AGENCY, REGION 6</t>
-        </is>
-      </c>
+          <t>U.S. Army Corps of Engineers, Portland District</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr"/>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>Solicitation</t>
+          <t>Combined Synopsis/Solicitation (RFQ)</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
         <is>
-          <t>236220</t>
+          <t>541380</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>SBA Certified Women-Owned Small Business (WOSB) Program Set-Aside (FAR 19.15)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>46282</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>46288</v>
+          <t>Total Small Business Set-Aside</t>
+        </is>
+      </c>
+      <c r="I13" s="37" t="inlineStr"/>
+      <c r="J13" s="37" t="n">
+        <v>46290</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L13" s="15" t="inlineStr">
         <is>
-          <t>Denton, TX</t>
+          <t>USACE Portland District, Hydroelectric Design Center</t>
         </is>
       </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
-          <t>Construct and renovate the FEMA Region 6 Regional Watch Center at 800 N Loop 288, Denton TX; firm fixed price RFP.</t>
+          <t>No additional caveat recorded; official notice controls.</t>
         </is>
       </c>
       <c r="N13" s="18" t="inlineStr">
@@ -1713,61 +2354,51 @@
     <row r="14" ht="72" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>IT Services &amp; Equipment</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>Replace Window B4311</t>
+          <t>CFBLNET</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>FA466126R0011</t>
+          <t>HC104709250103</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>FA4661 7 CONS CD</t>
-        </is>
-      </c>
+          <t>Defense Information Systems Agency (DISA)</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr"/>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>Solicitation</t>
+          <t>Sources Sought</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>236220</t>
+          <t>541512</t>
         </is>
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>Total Small Business Set-Aside (FAR 19.5)</t>
-        </is>
-      </c>
-      <c r="I14" s="21" t="n">
-        <v>46267</v>
-      </c>
-      <c r="J14" s="21" t="n">
-        <v>46287</v>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I14" s="38" t="inlineStr"/>
+      <c r="J14" s="38" t="n">
+        <v>46295</v>
       </c>
       <c r="K14" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
-        <is>
-          <t>Dyess AFB, TX 79607</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="L14" s="19" t="inlineStr"/>
       <c r="M14" s="19" t="inlineStr">
         <is>
-          <t>Remove and replace 6 window sections (12 awning windows) at Bldg 4311, Dyess AFB, with new aluminum fixed-frame assemblies; proposals due Sep 22, 2026.</t>
+          <t>CFBLNet Design, Transition, and Operation (DTO) capabilities for USAF Mission Partner Capabilities Office and NATO/coalition MPE initiatives. Sources Sought; Response Date Sep 30, 2026 4:00 PM EDT; published Sep 17, 2026. Directly verified via browser.open on SAM.gov this turn.</t>
         </is>
       </c>
       <c r="N14" s="22" t="inlineStr">
@@ -1779,61 +2410,51 @@
     <row r="15" ht="72" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>IT Services &amp; Equipment</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Patten Hall Renovations - United States Merchant Marine Academy (USMMA)</t>
+          <t>DA01-Compensation &amp; Pension (C&amp;P) Product Line Help Desk Tier 2 and Deployment Support Services 2.0</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>6923G226Q000034</t>
+          <t>36C10B26Q0725</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>TRANSPORTATION, DEPARTMENT OF</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>DOT MARITIME ADMINISTRATION, USMMA Procurement</t>
-        </is>
-      </c>
+          <t>Department of Veterans Affairs</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr"/>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>Combined Synopsis/Solicitation</t>
+          <t>Sources Sought</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
         <is>
-          <t>236220</t>
+          <t>541512</t>
         </is>
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>Total Small Business Set-Aside (FAR 19.5)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>46260</v>
-      </c>
-      <c r="J15" s="17" t="n">
-        <v>46287</v>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I15" s="37" t="inlineStr"/>
+      <c r="J15" s="37" t="n">
+        <v>46296</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" s="15" t="inlineStr">
-        <is>
-          <t>Kings Point, NY 11024</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="L15" s="15" t="inlineStr"/>
       <c r="M15" s="15" t="inlineStr">
         <is>
-          <t>Renovate Patten Hall incl. medical clinic at USMMA, Kings Point NY: floors, walls, ceilings, doors, lead and asbestos abatement, painting, ADA ramp, plumbing, backup generator; historic-property standards apply.</t>
+          <t>Active Sources Sought / RFI; Response Date Oct 01, 2026 10:00 AM EDT; published Sep 17, 2026; draft PWS attached.</t>
         </is>
       </c>
       <c r="N15" s="18" t="inlineStr">
@@ -1845,29 +2466,25 @@
     <row r="16" ht="72" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>Janitorial &amp; Facilities</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>Repair Water Tanks Deficiencies</t>
+          <t>Kansas FY27 Mass Solicitation - Custodial Services</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>36C24826R0133</t>
+          <t>W912DQ27QA001</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>VETERANS AFFAIRS, DEPARTMENT OF</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>248-NETWORK CONTRACT OFFICE 8 (36C248)</t>
-        </is>
-      </c>
+          <t>US Army Corps of Engineers, Kansas City District</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr"/>
       <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Solicitation</t>
@@ -1875,31 +2492,29 @@
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>236220</t>
+          <t>561720</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>Service-Disabled Veteran-Owned Small Business (SDVOSB) Set-Aside (FAR 19.14); exclusively for VISN 8 Caribbean Construction MATOC IDIQ holders</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="n">
-        <v>46282</v>
-      </c>
-      <c r="J16" s="21" t="n">
-        <v>46289</v>
+          <t>Total Small Business Set-Aside (FAR 19.5)</t>
+        </is>
+      </c>
+      <c r="I16" s="38" t="inlineStr"/>
+      <c r="J16" s="38" t="n">
+        <v>46297</v>
       </c>
       <c r="K16" s="19" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L16" s="19" t="inlineStr">
         <is>
-          <t>San Juan, PR</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="M16" s="19" t="inlineStr">
         <is>
-          <t>Design/build services for Repair Water Tanks Deficiencies (Project 672-26-110) at the VA Caribbean Healthcare System, San Juan PR.</t>
+          <t>Mass solicitation covering ten custodial packages at recreation areas and facilities across five Kansas lake projects (Melvern Lake CDAR/Turkey Point, Pomona Lake Wolf Creek, etc.); each package may be awarded separately. Quotes due October 2, 2026 by 12:00 PM. Verified via fresh search hits (GovTribe listing + NWD USACE contracting opportunities page). Direct SAM.gov notice URL not recoverable this turn; url is the official USACE Northwestern Division contracting opportunities page listing the notice.</t>
         </is>
       </c>
       <c r="N16" s="22" t="inlineStr">
@@ -1911,29 +2526,25 @@
     <row r="17" ht="72" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>Building Construction</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>REPAIR LIVE FIRE TRAINING FACILITY AIRCRAFT MOCK-UP</t>
+          <t>iHouse Apartment Construction</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>FA665626R0006</t>
+          <t>75H70126R00026</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>DEPT OF THE AIR FORCE, AIR FORCE RESERVE COMMAND, FA6656 910 AW LGC</t>
-        </is>
-      </c>
+          <t>Department of Health and Human Services, Indian Health Service</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr"/>
       <c r="F17" s="15" t="inlineStr">
         <is>
           <t>Solicitation</t>
@@ -1946,26 +2557,24 @@
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>SBA Certified Women-Owned Small Business (WOSB) Program Set-Aside (FAR 19.15)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="n">
-        <v>46282</v>
-      </c>
-      <c r="J17" s="17" t="n">
-        <v>46290</v>
+          <t>Indian Small Business Economic Enterprise (ISBEE)</t>
+        </is>
+      </c>
+      <c r="I17" s="37" t="inlineStr"/>
+      <c r="J17" s="37" t="n">
+        <v>46303</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="L17" s="15" t="inlineStr">
         <is>
-          <t>Youngstown, OH</t>
+          <t>Tonalea, AZ 86044</t>
         </is>
       </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
-          <t>Repair and corrective work to the Aircraft Fire Training Facility aircraft mock-up at Youngstown Air Reserve Station: burners, ignition, structural steel, corrosion, sprinkler, propane and control systems.</t>
+          <t>No additional caveat recorded; official notice controls.</t>
         </is>
       </c>
       <c r="N17" s="18" t="inlineStr">
@@ -1974,14 +2583,132 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="72" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Food &amp; Bakery</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>FCI FORT DIX FY26 2ND QTR SUBSISTENCE; INCLUDING EGGS, BREAD AND DAIRY</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>15BFTD26Q00000001</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Department of Justice, Federal Bureau of Prisons, FCI Fort Dix</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr"/>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>Solicitation (Original)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>311999</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="inlineStr">
+        <is>
+          <t>Total Small Business Set-Aside (FAR 19.5)</t>
+        </is>
+      </c>
+      <c r="I18" s="38" t="n">
+        <v>45974</v>
+      </c>
+      <c r="J18" s="38" t="n">
+        <v>46346</v>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>63</v>
+      </c>
+      <c r="L18" s="19" t="inlineStr">
+        <is>
+          <t>Joint Base MDL, NJ 08641, USA</t>
+        </is>
+      </c>
+      <c r="M18" s="19" t="inlineStr">
+        <is>
+          <t>Title cross-confirmed via GovWin indexing of the same notice ID. Solicitation covers subsistence for the inmate population including bread line items 198-200 (hot dog, hamburger, whole wheat). Bread quoted as a combined line-item group. Quotes must be emailed to aaponteberrios@bop.gov (CC bvirgillo@bop.gov) in Excel format with SF-1449 and Contractor Information Sheet.</t>
+        </is>
+      </c>
+      <c r="N18" s="22" t="inlineStr">
+        <is>
+          <t>Open notice</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="72" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>IT Services &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>DCSA Innovation Gateway</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>HS0021-26-CSO-DCSA</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Defense Counterintelligence and Security Agency</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr"/>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>541512</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I19" s="37" t="inlineStr"/>
+      <c r="J19" s="37" t="n">
+        <v>48021</v>
+      </c>
+      <c r="K19" s="15" t="n">
+        <v>1738</v>
+      </c>
+      <c r="L19" s="15" t="inlineStr"/>
+      <c r="M19" s="15" t="inlineStr">
+        <is>
+          <t>Active competitive commercial solutions opening for prototype projects under Other Transaction Agreements (digital transformation enablement, data integration and advanced analytics, cyber and industrial security). Proposals accepted only in response to separately published Innovation Calls (e.g., Innovation Call #01 published 09/10/2026). Date offers due Jun 22, 2031.</t>
+        </is>
+      </c>
+      <c r="N19" s="18" t="inlineStr">
+        <is>
+          <t>Open notice</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:N17"/>
+  <autoFilter ref="A4:N19"/>
   <mergeCells count="3">
     <mergeCell ref="F3:J3"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="K5:K17">
+  <conditionalFormatting sqref="K5:K19">
     <cfRule type="cellIs" priority="1" operator="lessThanOrEqual" dxfId="0">
       <formula>7</formula>
     </cfRule>
@@ -2004,19 +2731,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;8 USA Government Contract Opportunities • snapshot 2026-09-18</oddFooter>
+    <oddFooter>&amp;C&amp;8 TenderTrack USA Opportunities • verified 2026-09-18</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2146,7 +2875,7 @@
           <t>California</t>
         </is>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="37" t="n">
         <v>46301</v>
       </c>
       <c r="G5" s="15" t="n">
@@ -2204,7 +2933,7 @@
           <t>California</t>
         </is>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="F6" s="38" t="n">
         <v>46294</v>
       </c>
       <c r="G6" s="19" t="n">
@@ -2262,7 +2991,7 @@
           <t>North Carolina</t>
         </is>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="37" t="n">
         <v>46300</v>
       </c>
       <c r="G7" s="15" t="n">
@@ -2320,7 +3049,7 @@
           <t>Illinois</t>
         </is>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F8" s="38" t="n">
         <v>46317</v>
       </c>
       <c r="G8" s="19" t="n">
@@ -2378,7 +3107,7 @@
           <t>Ohio</t>
         </is>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="37" t="n">
         <v>46296</v>
       </c>
       <c r="G9" s="15" t="n">
@@ -2436,7 +3165,7 @@
           <t>Iowa</t>
         </is>
       </c>
-      <c r="F10" s="21" t="n">
+      <c r="F10" s="38" t="n">
         <v>46293</v>
       </c>
       <c r="G10" s="19" t="n">
@@ -2494,7 +3223,7 @@
           <t>California</t>
         </is>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="37" t="n">
         <v>46303</v>
       </c>
       <c r="G11" s="15" t="n">
@@ -2552,7 +3281,7 @@
           <t>California</t>
         </is>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="38" t="n">
         <v>46335</v>
       </c>
       <c r="G12" s="19" t="n">
@@ -2610,7 +3339,7 @@
           <t>Maryland</t>
         </is>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="37" t="n">
         <v>46301</v>
       </c>
       <c r="G13" s="15" t="n">
@@ -2664,7 +3393,7 @@
           <t>Missouri</t>
         </is>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="38" t="n">
         <v>46289</v>
       </c>
       <c r="G14" s="19" t="n">
@@ -2723,7 +3452,7 @@
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;8 USA Government Contract Opportunities • snapshot 2026-09-18</oddFooter>
+    <oddFooter>&amp;C&amp;8 TenderTrack USA Opportunities • verified 2026-09-18</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2859,7 +3588,7 @@
           <t>2026-09-22T12:00:00-04:00</t>
         </is>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="H5" s="37" t="n">
         <v>46283</v>
       </c>
       <c r="I5" s="18" t="inlineStr">
@@ -2904,7 +3633,7 @@
           <t>2026-09-30T12:00:00 (digital proposals); 2026-10-02T12:00:00 (sealed hard copy)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="n">
+      <c r="H6" s="38" t="n">
         <v>46283</v>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -2928,7 +3657,7 @@
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;8 USA Government Contract Opportunities • snapshot 2026-09-18</oddFooter>
+    <oddFooter>&amp;C&amp;8 TenderTrack USA Opportunities • verified 2026-09-18</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2941,6 +3670,4974 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>State Education Projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>16 state-level school and university construction and facilities projects individually verified open on September 18, 2026. Education IT hardware returned zero verified open bids across all 10 sweep states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="39" t="inlineStr">
+        <is>
+          <t>Recheck every deadline on the official posting before use, especially near-term dates. Records whose ad documents were read via a mirror must be verified in the official portal directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Issuer</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Opportunity Title</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Source / Source Type</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Direct Link</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Verification Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>University of Central Florida</t>
+        </is>
+      </c>
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>ITN2026-01NC Developer for University Mixed Use P3</t>
+        </is>
+      </c>
+      <c r="D5" s="40" t="inlineStr">
+        <is>
+          <t>2026-09-23 3:00 PM EST</t>
+        </is>
+      </c>
+      <c r="E5" s="40" t="inlineStr">
+        <is>
+          <t>UCF Procurement Services</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>UCF Procurement Services listing; developer solicitation for a university mixed-use public-private project with site surveys, easements, and environmental reports. Near-term deadline (September 23), recheck before use. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>Dormitory Authority of the State of New York (on behalf of CUNY Baruch College)</t>
+        </is>
+      </c>
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>CUNY Baruch College Newman Hall Facade Restoration and Hazardous Materials Abatement</t>
+        </is>
+      </c>
+      <c r="D6" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E6" s="41" t="inlineStr">
+        <is>
+          <t>NYS Contract Reporter</t>
+        </is>
+      </c>
+      <c r="F6" s="41" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G6" s="41" t="inlineStr">
+        <is>
+          <t>NYS Contract Reporter ad; time-of-day cutoff not shown on listing, check ad detail page. Eligibility limited to NYS certified minority, women, or small business enterprises; CR# 2139108. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>State University of New York (Binghamton)</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>SUNY Binghamton Construct Student Affairs Rehearsal Building</t>
+        </is>
+      </c>
+      <c r="D7" s="40" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E7" s="40" t="inlineStr">
+        <is>
+          <t>NYS Contract Reporter</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>NYS Contract Reporter ad; time-of-day cutoff not shown on listing, check ad detail page; CR# 2139119. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>Appalachian State University</t>
+        </is>
+      </c>
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>Main Steam Line Replacement and Vault Access</t>
+        </is>
+      </c>
+      <c r="D8" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-29 (Eastern Time; exact bid time not shown on official table)</t>
+        </is>
+      </c>
+      <c r="E8" s="41" t="inlineStr">
+        <is>
+          <t>UNC System: University Finance vendor opportunities page (official)</t>
+        </is>
+      </c>
+      <c r="F8" s="41" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>UNC System official open construction opportunities table; date only, exact bid time not shown, Eastern Time inferred. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>NC Agricultural and Technical State University</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>Upgrade Heating/Hot Water in Four Dormitories</t>
+        </is>
+      </c>
+      <c r="D9" s="40" t="inlineStr">
+        <is>
+          <t>2026-09-22 (Eastern Time; exact bid time not shown on official table)</t>
+        </is>
+      </c>
+      <c r="E9" s="40" t="inlineStr">
+        <is>
+          <t>UNC System: University Finance vendor opportunities page (official)</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>UNC System official open construction opportunities table; date only, exact bid time not shown, Eastern Time inferred. Near-term deadline (September 22), recheck before use. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="41" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B10" s="41" t="inlineStr">
+        <is>
+          <t>UNC Chapel Hill (Academic Affairs)</t>
+        </is>
+      </c>
+      <c r="C10" s="41" t="inlineStr">
+        <is>
+          <t>Bingham Facility Building 2 - Replace HVAC System (Revised)</t>
+        </is>
+      </c>
+      <c r="D10" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-24 (Eastern Time; exact bid time not shown on official table)</t>
+        </is>
+      </c>
+      <c r="E10" s="41" t="inlineStr">
+        <is>
+          <t>UNC System: University Finance vendor opportunities page (official)</t>
+        </is>
+      </c>
+      <c r="F10" s="41" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G10" s="41" t="inlineStr">
+        <is>
+          <t>UNC System official open construction opportunities table; date only, exact bid time not shown, Eastern Time inferred. Revised bid. Near-term deadline (September 24), recheck before use. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>UNC Chapel Hill (Academic Affairs)</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>FY25-27 Parking Decks Elevator Modernization</t>
+        </is>
+      </c>
+      <c r="D11" s="40" t="inlineStr">
+        <is>
+          <t>2026-09-29 (Eastern Time; exact bid time not shown on official table)</t>
+        </is>
+      </c>
+      <c r="E11" s="40" t="inlineStr">
+        <is>
+          <t>UNC System: University Finance vendor opportunities page (official)</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>UNC System official open construction opportunities table; date only, exact bid time not shown, Eastern Time inferred. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="41" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B12" s="41" t="inlineStr">
+        <is>
+          <t>UNC Chapel Hill (Academic Affairs)</t>
+        </is>
+      </c>
+      <c r="C12" s="41" t="inlineStr">
+        <is>
+          <t>Tate Turner Kuralt - Fire Alarm Replacement</t>
+        </is>
+      </c>
+      <c r="D12" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-30 (Eastern Time; exact bid time not shown on official table)</t>
+        </is>
+      </c>
+      <c r="E12" s="41" t="inlineStr">
+        <is>
+          <t>UNC System: University Finance vendor opportunities page (official)</t>
+        </is>
+      </c>
+      <c r="F12" s="41" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G12" s="41" t="inlineStr">
+        <is>
+          <t>UNC System official open construction opportunities table; date only, exact bid time not shown, Eastern Time inferred. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>UNC Greensboro</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>Spring Garden Apartments HVAC &amp; Roofing Replacement - Re-Bid</t>
+        </is>
+      </c>
+      <c r="D13" s="40" t="inlineStr">
+        <is>
+          <t>2026-10-01 (Eastern Time; exact bid time not shown on official table)</t>
+        </is>
+      </c>
+      <c r="E13" s="40" t="inlineStr">
+        <is>
+          <t>UNC System: University Finance vendor opportunities page (official)</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>UNC System official open construction opportunities table; date only, exact bid time not shown, Eastern Time inferred. Re-bid. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="41" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>Ionia Public Schools</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="inlineStr">
+        <is>
+          <t>Ionia Public Schools Secure Entry Projects</t>
+        </is>
+      </c>
+      <c r="D14" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-23T14:00:00-04:00 (Eastern Time)</t>
+        </is>
+      </c>
+      <c r="E14" s="41" t="inlineStr">
+        <is>
+          <t>Michigan SIGMA Vendor Self Service official posting, SIGMA ref RFP-IONI-260000002559-2 (document read via mirror; verify in SIGMA directly)</t>
+        </is>
+      </c>
+      <c r="F14" s="41" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G14" s="41" t="inlineStr">
+        <is>
+          <t>Michigan SIGMA Vendor Self Service official posting, SIGMA ref RFP-IONI-260000002559-2; ad document read via lightrfp mirror, verify in SIGMA directly. Sealed bids due 2:00 PM local time at O-A-K Operations Center, Caledonia, MI. Near-term deadline (September 23), recheck before use. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t>Kent Intermediate School District</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>KCTC Mechanical Improvements</t>
+        </is>
+      </c>
+      <c r="D15" s="40" t="inlineStr">
+        <is>
+          <t>2026-09-22T14:00:00-04:00 (Eastern Time)</t>
+        </is>
+      </c>
+      <c r="E15" s="40" t="inlineStr">
+        <is>
+          <t>Michigan SIGMA Vendor Self Service official posting, SIGMA ref RFP-KSD-260000002546-1 (document read via mirror; verify in SIGMA directly)</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>Michigan SIGMA Vendor Self Service official posting, SIGMA ref RFP-KSD-260000002546-1; ad document read via lightrfp mirror, verify in SIGMA directly. Sealed bids due 2:00 PM local time at O-A-K Operations Center, Caledonia, MI. Near-term deadline (September 22), recheck before use. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="41" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>Los Angeles Unified School District (LAUSD)</t>
+        </is>
+      </c>
+      <c r="C16" s="41" t="inlineStr">
+        <is>
+          <t>LAUSD Bid No. 2710046 - Hollywood High School Stair Replacement (PSA)</t>
+        </is>
+      </c>
+      <c r="D16" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-29T13:00:00-07:00 (bids due BEFORE 1:00 PM PDT)</t>
+        </is>
+      </c>
+      <c r="E16" s="41" t="inlineStr">
+        <is>
+          <t>LAUSD official bid advertisement (RAMP form), advertised 9/8/2026 and 9/14/2026 (document via mirror; verify in LAUSD supplier portal)</t>
+        </is>
+      </c>
+      <c r="F16" s="41" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G16" s="41" t="inlineStr">
+        <is>
+          <t>LAUSD official bid advertisement (RAMP form), advertised 9/8/2026 and 9/14/2026; document read via lightrfp mirror, verify in LAUSD supplier portal. Bids due before 1:00 PM PDT; B General Building Contractor license required; electronic bidding through the LAUSD Supplier Portal (Ariba). Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>Los Angeles Unified School District (LAUSD)</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>LAUSD Bid No. 2710049 - Castelar EEC Outdoor Classroom</t>
+        </is>
+      </c>
+      <c r="D17" s="40" t="inlineStr">
+        <is>
+          <t>2026-09-30T13:00:00-07:00 (bids due BEFORE 1:00 PM PDT)</t>
+        </is>
+      </c>
+      <c r="E17" s="40" t="inlineStr">
+        <is>
+          <t>LAUSD official bid advertisement (RAMP form), advertised 9/3/2026 and 9/8/2026 (document via mirror; verify in LAUSD supplier portal)</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>LAUSD official bid advertisement (RAMP form), advertised 9/3/2026 and 9/8/2026; document read via lightrfp mirror, verify in LAUSD supplier portal. Bids due before 1:00 PM PDT; B General Building Contractor license required; electronic bidding through the Ariba Business Network. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="41" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t>University of Illinois at Urbana-Champaign (Board of Trustees)</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t>Davenport Hall HVAC Upgrades (Project U24038)</t>
+        </is>
+      </c>
+      <c r="D18" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:00 America/Chicago</t>
+        </is>
+      </c>
+      <c r="E18" s="41" t="inlineStr">
+        <is>
+          <t>University of Illinois Plan Room (uiucplanroom.com) - Construction Jobs for Bid</t>
+        </is>
+      </c>
+      <c r="F18" s="41" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G18" s="41" t="inlineStr">
+        <is>
+          <t>Official Notice to Bidders (JobID 22582) at the University of Illinois Plan Room (uiucplanroom.com); listing showed 5 days remaining on 2026-09-18. Near-term deadline (September 23), recheck before use. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="40" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <t>University of Illinois at Urbana-Champaign (Board of Trustees)</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>North Campus Chiller Plant - Cooling Tower Replacement (Project U25074)</t>
+        </is>
+      </c>
+      <c r="D19" s="40" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:00 America/Chicago</t>
+        </is>
+      </c>
+      <c r="E19" s="40" t="inlineStr">
+        <is>
+          <t>University of Illinois Plan Room (uiucplanroom.com) - Construction Jobs for Bid</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>University of Illinois Plan Room listing; showed 13 days remaining on 2026-09-18; pre-bid was 2026-09-16. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="41" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>Pennsylvania Department of General Services / West Chester University</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t>West Chester University - Sturzebecker Health Science Center Renovations (DGS C-0414-0072 Phase 1)</t>
+        </is>
+      </c>
+      <c r="D20" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:00 America/New_York</t>
+        </is>
+      </c>
+      <c r="E20" s="41" t="inlineStr">
+        <is>
+          <t>PA DGS eMarketplace solicitation</t>
+        </is>
+      </c>
+      <c r="F20" s="41" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="G20" s="41" t="inlineStr">
+        <is>
+          <t>PA DGS eMarketplace solicitation on the DGS currently out to bid page; pre-bid held 2026-08-27; bids only via e-Builder. Verified 2026-09-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>Coverage: zero verified open IT hardware bids across all 10 sweep states (no laptops, Chromebooks, desktops, printers, or copiers with confirmed future deadlines; the category stays empty, not padded). Zero open prime or subcontracting notices found on official state portals. Ohio and Georgia produced zero verified records. All 16 records above are construction and facilities projects individually verified on September 18, 2026; recheck deadlines on the official postings before use.</t>
+        </is>
+      </c>
+      <c r="B22" s="45" t="n"/>
+      <c r="C22" s="45" t="n"/>
+      <c r="D22" s="45" t="n"/>
+      <c r="E22" s="45" t="n"/>
+      <c r="F22" s="45" t="n"/>
+      <c r="G22" s="45" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G20"/>
+  <mergeCells count="4">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId16"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recent Federal Awards</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>40 recent awards from the USAspending.gov API. These are closed awards and contractor evidence, not open bids. The date is the API-reported period-of-performance start date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Award / Contract ID</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Recipient</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>NAICS Query Code</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Reported Start Date</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Amount (USD)</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Verified On</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>USAspending Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Janitorial &amp; Facilities</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>1240BK25P0035</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>UMPQUA NATIONAL FOREST, TILLER RD JANITORIAL</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Department of Agriculture</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>ROGUE VALLEY H2O LLC</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>561720</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>2028-04-30</t>
+        </is>
+      </c>
+      <c r="H5" s="43" t="n">
+        <v>37531</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>IT Services &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>36C10M26F50060</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>AUDIO VISUAL EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Department of Veterans Affairs</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>CELLENTIA INFORMATION TECHNOLOGY COMPANY</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>541512</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>2027-08-27</t>
+        </is>
+      </c>
+      <c r="H6" s="44" t="n">
+        <v>294893.32</v>
+      </c>
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>IT Services &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>95C67826P0287</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>CONTRACT NO. DSCS-26-RFP-66 WITH MINDCUBED LLC FOR QA &amp; SOFTWARE TESTING SERVICES TO SUPPORT THE  IMPLEMENTATION OF DCCA CMS. POP: 7/13/2026 THROUGH 7/12/2027.</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>District of Columbia Courts</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>MINDCUBED LLC</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>541512</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>2027-07-12</t>
+        </is>
+      </c>
+      <c r="H7" s="43" t="n">
+        <v>366873.6</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>IT Services &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>273FCC26F0061</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>NEWS CLIPPING SERVICE</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Federal Communications Commission</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>ALLIANCE GLOBAL TECH INC.</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>541512</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>2027-06-14</t>
+        </is>
+      </c>
+      <c r="H8" s="44" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>80NSSC26P1530</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>ELI GROUP TRAINING</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>National Aeronautics and Space Administration</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>ELI GROUP, LLC</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>541611</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>2027-02-17</t>
+        </is>
+      </c>
+      <c r="H9" s="43" t="n">
+        <v>27500</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>IT Services &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>1305M226F0401</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>CENTRALIZED INTEGRATED REAL-TIME REPOSITORY FOR UNIFIED SERVICES (CIRRUS) PHASE 2 CAPABILITIES. THIS EFFORT SUPPORTS THE NOAA/NWS BY ADVANCING THE MIGRATION AND DEPLOYMENT OF OPERATIONAL WEATHER APPLICATION CAPABILITIES FROM LEGACY AWIPS ENVIRONMENTS</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Department of Commerce</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>BOOZ ALLEN HAMILTON INC</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>541512</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>2027-02-01</t>
+        </is>
+      </c>
+      <c r="H10" s="44" t="n">
+        <v>14130377.43</v>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>80NSSC26P1496</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>ELI GROUP (MTM) / 2027 POWER FORUM</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>National Aeronautics and Space Administration</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>ELI GROUP, LLC</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>541611</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>2027-01-27</t>
+        </is>
+      </c>
+      <c r="H11" s="43" t="n">
+        <v>27500</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Building Construction</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>1240LU26C0031</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>GAOA LCIC LIGHTING UPGRADE (RE-SOLICITATION)</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Department of Agriculture</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>LIBERTY ELECTRIC INC</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>236220</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="H12" s="44" t="n">
+        <v>664550</v>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>19AQMM26F1357</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>TORP 26-035 RPPR - GRANT SPECIALIST</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Department of State</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>MEC ENERGY SERVICES LLC</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>541611</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="H13" s="43" t="n">
+        <v>18110.4</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>80HQTR26F0014</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>TO OBTAIN AN INDEPENDENT, LICENSED ACCOUNTING FIRM TO REVIEW GRANT DOCUMENTS AND CHECK AND VERIFY IF A  PRIME CONTRACTOR IS PROPERLY FOLLOWING RESEARCH SECURITY RULES FOR SPECIFIC NASA GRANTS.</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>National Aeronautics and Space Administration</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>BROWN &amp; CO CERTIFIED PUBLIC ACCOUNTANTS &amp; MANAGEMENT CONSULTANTS PLLC</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>541611</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="H14" s="44" t="n">
+        <v>274103.69</v>
+      </c>
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>19AQMM26F0128</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>FUNDING IS REQUIRED TO PROVIDE CONSTRUCTION SECURITY PERSONNEL (TL AND TWO CSTS) FROM DECEMBER 1, 2026, THROUGH NOVEMBER 30, 2027.</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Department of State</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>IDS INTERNATIONAL GOVERNMENT SERVICES LLC</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>561612</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="H15" s="43" t="n">
+        <v>708882.26</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>75H70726P00133</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>SECURITY GUARD SERVICES- JSU</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Department of Health and Human Services</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>IRON HORSE SECURITY, LLC</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>561612</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="H16" s="44" t="n">
+        <v>99424</v>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>19AQMM26C0601</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>OVERSEAS GUARD UNIFORMED AND ARMED SERVICES ON BEHALF OF THE US AMERICAN MISSION LOME WHICH REQUIRES THE CONTRACTOR TO PREVENT LOSS OR INJURY TO U.S. PERSONNEL, DEPENDENTS, PROPERTY DESTRUCTION OF ASSETS TO PREVENT UNAUTHORIZED ACCESS AND DETER PO</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Department of State</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>INTER-CON SECURITY SYSTEMS, INC.</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>561612</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="H17" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J17" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Building Construction</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>FA462526F0023</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>REPLACE THE WATER SERVICE LINE, STEAM SUPPLY LINE, AND STEAM CONDENSATE LINE FOR B2014</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Department of Defense</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>DEFENDER CONTRACTING &amp; CONSTRUCTION 2, LLC</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>236220</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="H18" s="44" t="n">
+        <v>447648.97</v>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>19AQMM26F0802</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>SYSTEMS FURNITURE, CASEGOODS, SEATING &amp; ANCILLARY</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Department of State</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>GLACIER SUPPORT SERVICES, LLC</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>337127</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="H19" s="43" t="n">
+        <v>969705.8100000001</v>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>IT Services &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>75FCMC26F0144</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>CMS REQUIRES A MODERN, GOVERNMENT-OWNED, OPEN-SOURCE REPLACEMENT THAT DELIVERS THE SAME CONSUMER-FACING FUNCTIONALITY WITH GREATER FLEXIBILITY, TRANSPARENCY, AND LONG-TERM SUSTAINABILITY.</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Department of Health and Human Services</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>ORAN INC</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>541512</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="H20" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>80NSSC26FA532</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>THE PURPOSE OF THIS TASK ORDER IS TO PERFORM AN ISO 9001 SURVEILLANCE AUDIT AT KSC'S NASA FACILITY.</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>National Aeronautics and Space Administration</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>NATIONAL QUALITY ASSURANCE - U.S.A., INC.</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>541611</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="H21" s="43" t="n">
+        <v>9068</v>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>Medical Supplies</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>15B41226F00000176</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>FY26 B1 ARJO - SARA LIFT AUG 26</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>ARJO INC</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>339112</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="H22" s="44" t="n">
+        <v>26705.56</v>
+      </c>
+      <c r="I22" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Janitorial &amp; Facilities</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>12444126F0059</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>APPALACHIAN RD OFFICE AND WORKCENTER JANITORIAL SERVICES BPA CALL BASE</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Department of Agriculture</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>LINDA F HENSLEY</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>561720</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="H23" s="43" t="n">
+        <v>15446.92</v>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J23" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>Janitorial &amp; Facilities</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>47PE5626F0397</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>FEDERAL BUILDING AND US COURTHOUSE, FLINT, MI AND THE FEDERAL BUILDING IN SAGINAW, MI. ABOVE STANDARD SNOW REMOVAL SERVICES FOR FY27</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>General Services Administration</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>SVRC INDUSTRIES INC</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>561720</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="H24" s="44" t="n">
+        <v>23355.3</v>
+      </c>
+      <c r="I24" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>70RFP426FRE500007</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>PROTECTIVE SECURITY OFFICER (PSO) SERVICES THROUGHOUT THE STATE OF MICHIGAN</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Department of Homeland Security</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>UNIVERSAL PROTECTION SERVICE, LIMITED PARTNERSHIP</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>561612</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="H25" s="43" t="n">
+        <v>562676.58</v>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>70RFP426FRE700019</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>TASK ORDER ARMED FOR PROTECTIVE SECURITY OFFICER (PSO) SERVICES THROUGHOUT THE STATE OF ARKANSAS</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>Department of Homeland Security</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>KR-MTAC LLC</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>561612</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="H26" s="44" t="n">
+        <v>83474.77</v>
+      </c>
+      <c r="I26" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Food &amp; Bakery</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>15B41926P00000136</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>FY27 A1 ELWOOD QUARTERLY BID AWARD QTR 1  SOLICITATION WAS PUBLISHED ON UNISON MARKETPLACE BUY 1211820</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>ELWOOD INTERNATIONAL, INC</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>311999</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="H27" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>Food &amp; Bakery</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>15B41926P00000135</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>FY27 A1 SMOOTH SAILING QUARTERLY BID AWARD Q1  SOLICITATION WAS PUBLISHED ON UNISON MARKETPLACE BUY 1211820</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>THE SMOOTH SAILING GROUP LLC</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>311999</t>
+        </is>
+      </c>
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="H28" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Food &amp; Bakery</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>15B41926P00000134</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>FY27 A1 PUEBLO QUARTERLY BID AWARD QTR 1  SOLICITATION WAS PUBLISHED ON UNISON MARKETPLACE BUY 1211820</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>PUEBLO TRADING CO INC</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>311999</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="H29" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J29" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="56" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>Food &amp; Bakery</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>15B41926P00000133</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>FY27 A1 HIGHLAND QUARTERLY BID AWARD QTR 1  SOLICITATION WAS PUBLISHED ON UNISON MARKETPLACE BUY 1211820</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>HIGHLAND WHOLESALE FOODS, INC.</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>311999</t>
+        </is>
+      </c>
+      <c r="G30" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="H30" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Food &amp; Bakery</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>15B41926P00000132</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>FY27 A1 ADVANCED COM QUARTERLY BID AWARD QTR 1  SOLICITATION WAS PUBLISHED ON UNISON MARKETPLACE BUY 1211820</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>ADVANCED COMMODITIES, INC.</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>311999</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="H31" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J31" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="56" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>19AQMM26F1039</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>LOBBY SEATING</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>Department of State</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>GLACIER SUPPORT SERVICES, LLC</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>337127</t>
+        </is>
+      </c>
+      <c r="G32" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="H32" s="44" t="n">
+        <v>24144.24</v>
+      </c>
+      <c r="I32" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="56" customHeight="1">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>Medical Supplies</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>15B41226F00000169</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>FY26 B1 ARJO JK MAXI MOVE LIFT JUL 26</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>ARJO INC</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>339112</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="H33" s="43" t="n">
+        <v>39856.88</v>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J33" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="56" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>Building Construction</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>693JK426F96020N</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>DOT HQ - 07 &amp; 09 FURNITURE RECONFIGURATION - OPTION 2</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>Department of Transportation</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>EMCOR GOVERNMENT SERVICES, INC</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>236220</t>
+        </is>
+      </c>
+      <c r="G34" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H34" s="44" t="n">
+        <v>391595.37</v>
+      </c>
+      <c r="I34" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J34" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="56" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>Building Construction</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>36C25226N0584</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>TASK ORDER FOR CAMPUS SITE IMPROVEMENTS UNDER THE CONSTRUCTION MULTIPLE AWARD TASK ORDER CONTRACT (MATOC) FOR THE WM S. MIDDLETON VA HOSPITAL, MADISON WISCONSIN.</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>Department of Veterans Affairs</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>U.S. VET GENERAL CONTRACTING, LLC</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>236220</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H35" s="43" t="n">
+        <v>761563</v>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J35" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="56" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>Building Construction</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>W912QR26PA029</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>DOG CREEK SHOWER HOUSE RENOVATION</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>Department of Defense</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL SOLUTION LLC</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>236220</t>
+        </is>
+      </c>
+      <c r="G36" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H36" s="44" t="n">
+        <v>92657</v>
+      </c>
+      <c r="I36" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="56" customHeight="1">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>Janitorial &amp; Facilities</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>12444526P0078</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>MIDEWIN NATIONAL FOREST JANITORIAL CONTRACT</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>Department of Agriculture</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>ADA S. MCKINLEY COMMUNITY SERVICES, INC.</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>561720</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="H37" s="43" t="n">
+        <v>57216.64</v>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J37" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="56" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>15B51126F00000010</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>SCRO-TABLES-FOR-P0511</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>ACCESS SUPPLY LLC</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>337127</t>
+        </is>
+      </c>
+      <c r="G38" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H38" s="44" t="n">
+        <v>23031.45</v>
+      </c>
+      <c r="I38" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J38" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="56" customHeight="1">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Medical Supplies</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>15B41226F00000159</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>FY26 B1 ARJO JK MIRANTI POWER DRIVE SCALE JUL 26</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>ARJO INC</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>339112</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="H39" s="43" t="n">
+        <v>23829.62</v>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J39" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="56" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>Medical Supplies</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>15B41226P00000195</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>FY26 B1 ARJO JK STILL BATH ASSEM CONNECT JUL 26</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>ARJO INC</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>339112</t>
+        </is>
+      </c>
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="H40" s="44" t="n">
+        <v>28479.32</v>
+      </c>
+      <c r="I40" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="56" customHeight="1">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>Medical Supplies</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>15BPCC26F00000146</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>BD PYXIS AUTOMATED MEDICATION DISPENSING CABINETS</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>FOUR POINTS TECHNOLOGY, L.L.C.</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>339112</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H41" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J41" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="56" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>Janitorial &amp; Facilities</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>140R1026P0008</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>NEWELL BLDG JANITORIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Department of the Interior</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>THINK FORWARD SOLUTIONS, LLC</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>561720</t>
+        </is>
+      </c>
+      <c r="G42" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H42" s="44" t="n">
+        <v>45546</v>
+      </c>
+      <c r="I42" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J42" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="56" customHeight="1">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>49100426F0096</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>EXECUTIVE TRANSPORTATION TASK ORDER 39 - INTERIOR OUTFITTING AND OFFICE MOVE SERVICES IDIQ SUPPORT SERVICES</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>National Science Foundation</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>HERITAGE INTERIORS LLC</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>337127</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H43" s="43" t="n">
+        <v>290171.25</v>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J43" s="18" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="56" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>49100426F0077</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>TO#38 - SENIOR PROGRAM MANAGER - INTERIOR OUTFITTING AND OFFICE MOVE SERVICES IDIQ SUPPORT SERVICES</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>National Science Foundation</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>HERITAGE INTERIORS LLC</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>337127</t>
+        </is>
+      </c>
+      <c r="G44" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H44" s="44" t="n">
+        <v>349862.4</v>
+      </c>
+      <c r="I44" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J44" s="22" t="inlineStr">
+        <is>
+          <t>Open award record</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:J44"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId40"/>
+  </hyperlinks>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 TenderTrack USA Opportunities • verified 2026-09-18</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId41"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Upcoming Acquisition Forecasts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>12 DHS Acquisition Planning Forecast System records. These are planning forecasts, not open bids; timing and scope may change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Forecast ID</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Program / Requirement</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Estimated Solicitation / Award Timing</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Verified On</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Official Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="66" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Building Construction</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>apfs-74828-sonoita-bps</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>New 200-Agent Sonoita, AZ Border Patrol Station</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>U.S. Customs and Border Protection (CBP)</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>236220</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Q4 FY2026 est. solicitation (release target 2026-09-09; anticipated award Q1 FY2027)</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Forecast, not open bid</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>Open forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>Building Construction</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>F2026072578</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>Design Build 100 Agent Presidio Border Patrol Station</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>U.S. Customs and Border Protection (CBP), Office of Administration</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>236220</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>Q4 FY2026 est. solicitation (release target 2026-07-24; anticipated award Q4 FY2026)</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>Forecast, not open bid</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>Open forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="66" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>F2026073278</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>HSI Data and Analytical Support Services</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>U.S. Immigration and Customs Enforcement (ICE), Homeland Security Investigations (HSI)</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>561450</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Q4 FY2026 est. solicitation (release target 2026-08-24; anticipated award Q4 FY2026)</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Forecast, not open bid</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>Open forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="66" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>F2024067049</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Terrorism and Targeted Violence Risk Mitigation</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Cybersecurity and Infrastructure Security Agency (CISA), DHS Headquarters</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>541611</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>Q1 FY2027 est. solicitation (release target 2026-10-19; anticipated award Q2 FY2027)</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>Forecast, not open bid</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>Open forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>IT Services &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>F2025071025</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Modular Mobile Surveillance System (M2S2)</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>U.S. Customs and Border Protection (CBP), Headquarters</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>334511</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Q3 FY2026 est. solicitation (release target 2026-04-15; anticipated award Q1 FY2027)</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>Forecast, not open bid</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>Open forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>apfs-73314-security-support-services-3s</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>Security Support Services (3S)</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>U.S. Citizenship and Immigration Services (USCIS), Office of Security and Integrity</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>541611</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>Q4 FY2026 est. solicitation (release target 2026-08-14; anticipated award Q1 FY2027)</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>Forecast, not open bid</t>
+        </is>
+      </c>
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>Open forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>F2026073616</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Visual Arts Support Services</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Federal Emergency Management Agency (FEMA), U.S. Fire Administration</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>541430</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Q4 FY2026 est. solicitation (release target 2026-07-01; anticipated award Q1 FY2027)</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>Forecast, not open bid</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>Open forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="66" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>F2024067961</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Records Operations Support Services (ROSS) for the USCIS National Records Center and Harrisonburg File Storage Facility</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>U.S. Citizenship and Immigration Services (USCIS)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>561110</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>Q4 FY2026 est. solicitation (release target 2026-09-11; anticipated award Q2 FY2027)</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>Forecast, not open bid</t>
+        </is>
+      </c>
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>Open forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>F2026075521</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>ERO OVERWATCH AND NATIONAL SECURITY ENFORCEMENT (ERO ONE) - Intelligence Research Specialists Professional Support Services</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>U.S. Immigration and Customs Enforcement (ICE), Enforcement and Removal Operations (ERO)</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>541611</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Q1 FY2027 est. solicitation (release target 2026-12-10; anticipated award Q2 FY2027)</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>Forecast, not open bid</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>Open forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Building Construction</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>apfs-67219-kodiak-door-hanger-3</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Repair Door Hanger 3 at Kodiak, AK (6849317)</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>U.S. Coast Guard (USCG), Shore Infrastructure Logistics Center</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>236220</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>Q4 FY2027 est. solicitation (release target 2027-08-01; anticipated award Q1 FY2028)</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>Forecast, not open bid</t>
+        </is>
+      </c>
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>Open forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Building Construction</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>F2026075449</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Leasing of Turnkey Modular Units</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>U.S. Immigration and Customs Enforcement (ICE), Management and Administration</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Q4 FY2026 est. solicitation (release target 2026-09-09; anticipated award Q4 FY2026)</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>Forecast, not open bid</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>Open forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>apfs-63249-cisa-communications-support</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Communications &amp; Support Services</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Cybersecurity and Infrastructure Security Agency (CISA), Office of External Affairs</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>541613</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>Q4 FY2026 est. solicitation (release target 2026-09-01; anticipated award Q4 FY2026)</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>Forecast, not open bid</t>
+        </is>
+      </c>
+      <c r="H16" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>Open forecast</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:I16"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId12"/>
+  </hyperlinks>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 TenderTrack USA Opportunities • verified 2026-09-18</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recent Winning Contractors</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>34 contractors derived from the 40-award USAspending snapshot. This is evidence of recent awards, not a complete contractor directory or an endorsement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Awards in This Dataset</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Total Value in Dataset (USD)</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Awarding Agencies</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Contract / Award IDs</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Source Scope</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Example Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>BOOZ ALLEN HAMILTON INC</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="43" t="n">
+        <v>14130377.43</v>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Department of Commerce</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>IT Services &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>1305M226F0401</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="62" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>GLACIER SUPPORT SERVICES, LLC</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="44" t="n">
+        <v>993850.05</v>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Department of State</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>19AQMM26F0802; 19AQMM26F1039</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="62" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>U.S. VET GENERAL CONTRACTING, LLC</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="43" t="n">
+        <v>761563</v>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Department of Veterans Affairs</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Building Construction</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>36C25226N0584</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="62" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>IDS INTERNATIONAL GOVERNMENT SERVICES LLC</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="44" t="n">
+        <v>708882.26</v>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Department of State</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>19AQMM26F0128</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>LIBERTY ELECTRIC INC</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="43" t="n">
+        <v>664550</v>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Department of Agriculture</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Building Construction</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>1240LU26C0031</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>HERITAGE INTERIORS LLC</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="44" t="n">
+        <v>640033.65</v>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>National Science Foundation</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>49100426F0096; 49100426F0077</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="62" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>UNIVERSAL PROTECTION SERVICE, LIMITED PARTNERSHIP</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="43" t="n">
+        <v>562676.58</v>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Department of Homeland Security</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>70RFP426FRE500007</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>DEFENDER CONTRACTING &amp; CONSTRUCTION 2, LLC</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="44" t="n">
+        <v>447648.97</v>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Department of Defense</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Building Construction</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>FA462526F0023</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="62" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>EMCOR GOVERNMENT SERVICES, INC</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="43" t="n">
+        <v>391595.37</v>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Department of Transportation</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Building Construction</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>693JK426F96020N</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="62" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>MINDCUBED LLC</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="44" t="n">
+        <v>366873.6</v>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>District of Columbia Courts</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>IT Services &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>95C67826P0287</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="62" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>CELLENTIA INFORMATION TECHNOLOGY COMPANY</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="43" t="n">
+        <v>294893.32</v>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Department of Veterans Affairs</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>IT Services &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>36C10M26F50060</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="62" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>BROWN &amp; CO CERTIFIED PUBLIC ACCOUNTANTS &amp; MANAGEMENT CONSULTANTS PLLC</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="44" t="n">
+        <v>274103.69</v>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>National Aeronautics and Space Administration</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>80HQTR26F0014</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="62" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>ALLIANCE GLOBAL TECH INC.</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="43" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Federal Communications Commission</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>IT Services &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>273FCC26F0061</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="62" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>ARJO INC</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="44" t="n">
+        <v>118871.38</v>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Medical Supplies</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>15B41226F00000176; 15B41226F00000169; 15B41226F00000159; 15B41226P00000195</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="62" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>IRON HORSE SECURITY, LLC</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="43" t="n">
+        <v>99424</v>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Department of Health and Human Services</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>75H70726P00133</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="62" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL SOLUTION LLC</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="44" t="n">
+        <v>92657</v>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Department of Defense</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>Building Construction</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>W912QR26PA029</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="62" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>KR-MTAC LLC</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="43" t="n">
+        <v>83474.77</v>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Department of Homeland Security</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>70RFP426FRE700019</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="62" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>ADA S. MCKINLEY COMMUNITY SERVICES, INC.</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="44" t="n">
+        <v>57216.64</v>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>Department of Agriculture</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Janitorial &amp; Facilities</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>12444526P0078</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="62" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>ELI GROUP, LLC</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="43" t="n">
+        <v>55000</v>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>National Aeronautics and Space Administration</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>80NSSC26P1530; 80NSSC26P1496</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H23" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="62" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>THINK FORWARD SOLUTIONS, LLC</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="44" t="n">
+        <v>45546</v>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>Department of the Interior</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Janitorial &amp; Facilities</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>140R1026P0008</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="62" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>ROGUE VALLEY H2O LLC</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="43" t="n">
+        <v>37531</v>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Department of Agriculture</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>Janitorial &amp; Facilities</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>1240BK25P0035</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="62" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>SVRC INDUSTRIES INC</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="44" t="n">
+        <v>23355.3</v>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>General Services Administration</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Janitorial &amp; Facilities</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>47PE5626F0397</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="62" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>ACCESS SUPPLY LLC</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="43" t="n">
+        <v>23031.45</v>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>15B51126F00000010</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="62" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>MEC ENERGY SERVICES LLC</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="44" t="n">
+        <v>18110.4</v>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>Department of State</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>19AQMM26F1357</t>
+        </is>
+      </c>
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="62" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>LINDA F HENSLEY</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="43" t="n">
+        <v>15446.92</v>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>Department of Agriculture</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Janitorial &amp; Facilities</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>12444126F0059</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H29" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="62" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>NATIONAL QUALITY ASSURANCE - U.S.A., INC.</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="44" t="n">
+        <v>9068</v>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>National Aeronautics and Space Administration</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>80NSSC26FA532</t>
+        </is>
+      </c>
+      <c r="G30" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="62" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>ORAN INC</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Department of Health and Human Services</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>IT Services &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>75FCMC26F0144</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H31" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="62" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>FOUR POINTS TECHNOLOGY, L.L.C.</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>Medical Supplies</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>15BPCC26F00000146</t>
+        </is>
+      </c>
+      <c r="G32" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="62" customHeight="1">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>INTER-CON SECURITY SYSTEMS, INC.</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Department of State</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>19AQMM26C0601</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="62" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>ELWOOD INTERNATIONAL, INC</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>Food &amp; Bakery</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>15B41926P00000136</t>
+        </is>
+      </c>
+      <c r="G34" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="62" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>THE SMOOTH SAILING GROUP LLC</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>Food &amp; Bakery</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>15B41926P00000135</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="62" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>PUEBLO TRADING CO INC</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>Food &amp; Bakery</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
+        <is>
+          <t>15B41926P00000134</t>
+        </is>
+      </c>
+      <c r="G36" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="62" customHeight="1">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>HIGHLAND WHOLESALE FOODS, INC.</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>Food &amp; Bakery</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>15B41926P00000133</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="62" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>ADVANCED COMMODITIES, INC.</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>Department of Justice</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>Food &amp; Bakery</t>
+        </is>
+      </c>
+      <c r="F38" s="19" t="inlineStr">
+        <is>
+          <t>15B41926P00000132</t>
+        </is>
+      </c>
+      <c r="G38" s="19" t="inlineStr">
+        <is>
+          <t>Derived only from 40 verified recent awards in this workbook</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>Open example award</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H38"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId34"/>
+  </hyperlinks>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 TenderTrack USA Opportunities • verified 2026-09-18</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId35"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3014,7 +8711,7 @@
           <t>Alabama Buys</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Not fully verified</t>
         </is>
@@ -3046,7 +8743,7 @@
           <t>Alaska Online Public Notices</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3078,7 +8775,7 @@
           <t>Arizona Procurement Portal (APP)</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3110,7 +8807,7 @@
           <t>ARBuy</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3142,7 +8839,7 @@
           <t>Cal eProcure</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3174,7 +8871,7 @@
           <t>ColoradoVSS</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3206,7 +8903,7 @@
           <t>CTsource</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3238,7 +8935,7 @@
           <t>MyMarketplace</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3270,7 +8967,7 @@
           <t>Vendor Information Portal</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3302,7 +8999,7 @@
           <t>Georgia Procurement Registry</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3334,7 +9031,7 @@
           <t>HIePRO</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3366,7 +9063,7 @@
           <t>IPRO (Idaho e Procurement System)</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>Not fully verified</t>
         </is>
@@ -3398,7 +9095,7 @@
           <t>BidBuy</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3430,7 +9127,7 @@
           <t>Indiana Supplier Portal</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>Login required</t>
         </is>
@@ -3462,7 +9159,7 @@
           <t>Iowa Bid Opportunities</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3494,7 +9191,7 @@
           <t>Kansas Supplier Portal</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3526,7 +9223,7 @@
           <t>Kentucky Vendor Self Service (VSS)</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3558,7 +9255,7 @@
           <t>LaPAC</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>Not fully verified</t>
         </is>
@@ -3590,7 +9287,7 @@
           <t>Maine Vendor Self Service (VSS)</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3622,7 +9319,7 @@
           <t>eMMA</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3654,7 +9351,7 @@
           <t>COMMBUYS</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3686,7 +9383,7 @@
           <t>SIGMA Vendor Self Service (SIGMA VSS)</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3718,7 +9415,7 @@
           <t>Minnesota OSP (SWIFT Supplier Portal)</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3750,7 +9447,7 @@
           <t>MAGIC</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="25" t="inlineStr">
         <is>
           <t>Not fully verified</t>
         </is>
@@ -3782,7 +9479,7 @@
           <t>MissouriBUYS</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3814,7 +9511,7 @@
           <t>eMACS</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>Login required</t>
         </is>
@@ -3846,7 +9543,7 @@
           <t>Nebraska Materiel Bid Opportunities</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3878,7 +9575,7 @@
           <t>NevadaEPro</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C32" s="25" t="inlineStr">
         <is>
           <t>Partial public access</t>
         </is>
@@ -3910,7 +9607,7 @@
           <t>NH Bids and Contracts</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -3942,7 +9639,7 @@
           <t>NJSTART</t>
         </is>
       </c>
-      <c r="C34" s="25" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>Login required</t>
         </is>
@@ -3974,7 +9671,7 @@
           <t>Euna Supplier Network (Bonfire)</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="25" t="inlineStr">
         <is>
           <t>Not fully verified</t>
         </is>
@@ -4006,7 +9703,7 @@
           <t>NYS Contract Reporter</t>
         </is>
       </c>
-      <c r="C36" s="25" t="inlineStr">
+      <c r="C36" s="27" t="inlineStr">
         <is>
           <t>Login required</t>
         </is>
@@ -4038,7 +9735,7 @@
           <t>eVP (Electronic Vendor Portal)</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -4070,7 +9767,7 @@
           <t>NDBuys</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -4102,7 +9799,7 @@
           <t>OhioBuys</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -4134,7 +9831,7 @@
           <t>Oklahoma Supplier Portal</t>
         </is>
       </c>
-      <c r="C40" s="23" t="inlineStr">
+      <c r="C40" s="25" t="inlineStr">
         <is>
           <t>Partial public access</t>
         </is>
@@ -4166,7 +9863,7 @@
           <t>OregonBuys</t>
         </is>
       </c>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -4198,7 +9895,7 @@
           <t>PA eMarketplace</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -4230,7 +9927,7 @@
           <t>Ocean State Procures</t>
         </is>
       </c>
-      <c r="C43" s="23" t="inlineStr">
+      <c r="C43" s="25" t="inlineStr">
         <is>
           <t>Partial public access</t>
         </is>
@@ -4262,7 +9959,7 @@
           <t>SC Vendor Portal</t>
         </is>
       </c>
-      <c r="C44" s="23" t="inlineStr">
+      <c r="C44" s="25" t="inlineStr">
         <is>
           <t>Not fully verified</t>
         </is>
@@ -4294,7 +9991,7 @@
           <t>Central portal not confirmed</t>
         </is>
       </c>
-      <c r="C45" s="23" t="inlineStr">
+      <c r="C45" s="25" t="inlineStr">
         <is>
           <t>Not fully verified</t>
         </is>
@@ -4326,7 +10023,7 @@
           <t>Edison Supplier Portal</t>
         </is>
       </c>
-      <c r="C46" s="25" t="inlineStr">
+      <c r="C46" s="27" t="inlineStr">
         <is>
           <t>Login required</t>
         </is>
@@ -4358,7 +10055,7 @@
           <t>ESBD (Electronic State Business Daily)</t>
         </is>
       </c>
-      <c r="C47" s="24" t="inlineStr">
+      <c r="C47" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -4390,7 +10087,7 @@
           <t>U3P (Bonfire)</t>
         </is>
       </c>
-      <c r="C48" s="24" t="inlineStr">
+      <c r="C48" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -4422,7 +10119,7 @@
           <t>Vermont Business Registry</t>
         </is>
       </c>
-      <c r="C49" s="24" t="inlineStr">
+      <c r="C49" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -4454,7 +10151,7 @@
           <t>eVA</t>
         </is>
       </c>
-      <c r="C50" s="24" t="inlineStr">
+      <c r="C50" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -4486,7 +10183,7 @@
           <t>WEBS</t>
         </is>
       </c>
-      <c r="C51" s="25" t="inlineStr">
+      <c r="C51" s="27" t="inlineStr">
         <is>
           <t>Login required</t>
         </is>
@@ -4518,7 +10215,7 @@
           <t>wvOASIS Vendor Self Service</t>
         </is>
       </c>
-      <c r="C52" s="24" t="inlineStr">
+      <c r="C52" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -4550,7 +10247,7 @@
           <t>VendorNet</t>
         </is>
       </c>
-      <c r="C53" s="24" t="inlineStr">
+      <c r="C53" s="26" t="inlineStr">
         <is>
           <t>Public search verified</t>
         </is>
@@ -4582,7 +10279,7 @@
           <t>Central portal not confirmed</t>
         </is>
       </c>
-      <c r="C54" s="23" t="inlineStr">
+      <c r="C54" s="25" t="inlineStr">
         <is>
           <t>Not fully verified</t>
         </is>
@@ -4660,7 +10357,7 @@
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;8 USA Government Contract Opportunities • snapshot 2026-09-18</oddFooter>
+    <oddFooter>&amp;C&amp;8 TenderTrack USA Opportunities • verified 2026-09-18</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4670,607 +10367,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId46"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Zero-to-Bid Roadmap</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Practical orientation for a person, LLC, company, or SMB. Requirements vary by buyer and solicitation; official notice terms control.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>Who Needs It</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>What to Prepare</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>Typical Timing / Rule</t>
-        </is>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>Do Not Miss</t>
-        </is>
-      </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>Official Route</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="72" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>Choose a business structure</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>Any seller</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>Ownership, state, registered agent, tax and liability plan</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>State-specific</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>An individual may sell in some settings, but entity and insurance requirements vary.</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>Use your state's official business filing office.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="72" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>Get EIN and business banking</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>Most businesses</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>Entity records, responsible-party information, bank account</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>Varies</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>Keep legal name and address consistent across records.</t>
-        </is>
-      </c>
-      <c r="G6" s="19" t="inlineStr">
-        <is>
-          <t>Use official IRS and bank channels.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>Register the entity in SAM.gov</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Federal prime bidders</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Legal business name, TIN, physical address, banking, NAICS, ownership, CAGE validation</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>Free; research found up to 10–12 business days; renew every 365 days</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>SAM registration is free. Do not share login credentials with a third party.</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>Open SAM.gov</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="72" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>Receive a UEI</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>Federal prime bidders</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>Issued through SAM registration</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>Often immediate if validation passes; manual review may take longer</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>A UEI-only record does not equal full registration for prime bidding.</t>
-        </is>
-      </c>
-      <c r="G8" s="22" t="inlineStr">
-        <is>
-          <t>Open SAM.gov</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="72" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>Select NAICS and check size</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Federal and many state bidders</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>Capabilities, revenue/employee size, relevant codes</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>Before bidding</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>A company can be small under one NAICS and not another.</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>Use SBA's official size standards.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>Assess certifications</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>Eligible small businesses</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>Ownership/control evidence, location, veteran or women-owned eligibility where applicable</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>Can take weeks or months</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>Never claim a certification or set-aside status you do not hold.</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>Use SBA certification channels.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="72" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Register on buyer portals</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>State/local and some prime subcontractors</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>Vendor profile, W-9, commodity codes, insurance, licenses</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>Portal-specific</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>Each state, county, city, authority, and prime may use a separate system.</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>Use the All 50 State Portals tab and official buyer links.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>Build a bid/no-bid checklist</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>Everyone</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>Capability match, past performance, staffing, pricing, schedule, bond/insurance capacity</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>Before every pursuit</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>Check notice type. Sources Sought and RFIs usually are not priced bid invitations.</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>Read the complete official notice and every amendment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Submit and retain proof</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Qualified bidders</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>Signed forms, pricing, technical response, reps/certs, attachments</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>Before exact deadline/time zone</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>Late submissions are commonly rejected. Follow the required channel exactly.</t>
-        </is>
-      </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>Use only the submission method named in the notice.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:G13"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId2"/>
-  </hyperlinks>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 USA Government Contract Opportunities • snapshot 2026-09-18</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Coverage, Definitions &amp; Caveats</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Read this sheet before treating the workbook as a complete market inventory.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>WHAT IS INCLUDED</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>13 federal notices individually confirmed open after September 18, 2026; 10 SBA SubNet notices with future closing dates; 2 K-12 school-district IT-hardware bids verified open on September 18, 2026; all 50 state procurement systems mapped with public-access status. Every external link was carried from the verified research dataset. This is a snapshot, not a live feed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1"/>
-    <row r="7" ht="34" customHeight="1"/>
-    <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
-        <is>
-          <t>WHAT IS NOT INCLUDED</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="B10" s="29" t="inlineStr">
-        <is>
-          <t>This is not every active SAM.gov notice, every city or county portal, every prime-contractor supplier portal, or every state solicitation. The federal collection pass ended early after a fetch-service failure. Facilities support, medical supplies, and general supplies/equipment contain zero verified rows in this version rather than guessed or stale listings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1"/>
-    <row r="12" ht="34" customHeight="1"/>
-    <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>NOTICE TYPES</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="31" t="inlineStr">
-        <is>
-          <t>Solicitation / Combined Synopsis-Solicitation: generally actionable competition; read the full package.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>Sources Sought / RFI: market research and capability discovery; usually not a priced bid invitation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="31" t="inlineStr">
-        <is>
-          <t>Commercial Solutions Opening: may stay open for an extended period and accept solutions under special procedures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>STATE DIRECTORY STATUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="B20" s="32" t="inlineStr">
-        <is>
-          <t>Public search verified: opportunity browsing was confirmed without login.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>Login required: official guidance routes users through authentication before search or response.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="B22" s="29" t="inlineStr">
-        <is>
-          <t>Partial: some information is public, but documents or response steps may require registration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="B23" s="29" t="inlineStr">
-        <is>
-          <t>Not fully verified: portal or no-login behavior could not be confirmed; blank URLs were intentionally not guessed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="B25" s="34" t="inlineStr">
-        <is>
-          <t>ACTION RULE</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="B26" s="27" t="inlineStr">
-        <is>
-          <t>Before bidding, open the official source and confirm that the notice remains active, review all amendments and attachments, verify eligibility and set-aside status, note the exact submission deadline and time zone, and use the buyer's required submission channel. A listed opportunity is not a promise of eligibility or award.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1"/>
-    <row r="28" ht="34" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B10:E12"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B26:E28"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B5:E7"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B14:E14"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 USA Government Contract Opportunities • snapshot 2026-09-18</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
 </file>